--- a/artfynd/A 30189-2022 artfynd.xlsx
+++ b/artfynd/A 30189-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30189-2022 artfynd.xlsx
+++ b/artfynd/A 30189-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131880387</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sandbacken, O, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>488934</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6520570</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>T-Ask-0046</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-03-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-03-16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu, David Tverling, Lovisa Larsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30189-2022 artfynd.xlsx
+++ b/artfynd/A 30189-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131880387</v>
       </c>
       <c r="B3" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30189-2022 artfynd.xlsx
+++ b/artfynd/A 30189-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131880387</v>
       </c>
       <c r="B3" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30189-2022 artfynd.xlsx
+++ b/artfynd/A 30189-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131880387</v>
       </c>
       <c r="B3" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30189-2022 artfynd.xlsx
+++ b/artfynd/A 30189-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131880387</v>
       </c>
       <c r="B3" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30189-2022 artfynd.xlsx
+++ b/artfynd/A 30189-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131880387</v>
       </c>
       <c r="B3" t="n">
-        <v>99054</v>
+        <v>99090</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30189-2022 artfynd.xlsx
+++ b/artfynd/A 30189-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131880387</v>
       </c>
       <c r="B3" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30189-2022 artfynd.xlsx
+++ b/artfynd/A 30189-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>131880387</v>
       </c>
       <c r="B3" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu, David Tverling, Lovisa Larsson</t>
+          <t>Lovisa Larsson, David Tverling, Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 30189-2022 artfynd.xlsx
+++ b/artfynd/A 30189-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>104230901</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489005.5374586224</v>
+        <v>489006</v>
       </c>
       <c r="R2" t="n">
-        <v>6520570.991933131</v>
+        <v>6520571</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2022-10-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,49 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131880387</v>
+        <v>95492659</v>
       </c>
       <c r="B3" t="n">
-        <v>99106</v>
+        <v>75428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandbacken, O, Nrk</t>
+          <t>Sandbacken Ö, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488934</v>
+        <v>488954</v>
       </c>
       <c r="R3" t="n">
-        <v>6520570</v>
+        <v>6520602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,11 +840,6 @@
           <t>Askersund</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>T-Ask-0046</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
           <t>2021-03-16</t>
@@ -880,26 +856,671 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>David Tverling, Lovisa Larsson, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113777472</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stora Björstorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>488995</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6520610</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113777468</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stora Björstorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>488995</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6520610</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt med spår på några döda granar. Nedre del av stammar</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>95492654</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sandbacken Ö, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>488935</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6520570</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-03-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-03-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>David Tverling, Lovisa Larsson, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>95492655</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sandbacken Ö, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>488977</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6520602</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-03-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-03-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>David Tverling, Lovisa Larsson, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131880387</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sandbacken, O, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>488934</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6520570</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>T-Ask-0046</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-03-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-03-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Sofia Lund</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Lovisa Larsson, David Tverling, Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu, David Tverling, Lovisa Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104230883</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skogarna runt Norra Bocksjön, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>488905</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6520556</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-10-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Måttligt mycket, frisk</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30189-2022 artfynd.xlsx
+++ b/artfynd/A 30189-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104230901</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>Miniforskningsresan Extensus Örebro län 2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95492659</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113777472</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113777468</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
           <t>Miniforskningsresan Extensus Örebro län 2021</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95492654</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Miniforskningsresan Extensus Örebro län 2021</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95492655</t>
         </is>
       </c>
     </row>
@@ -1419,6 +1454,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131880387</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1521,8 +1561,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104230883</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>